--- a/artfynd/A 56413-2025 artfynd.xlsx
+++ b/artfynd/A 56413-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119218696</v>
+        <v>119820313</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storholmsberget, Pi lm</t>
+          <t>Akkavare, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>687619</v>
+        <v>687718</v>
       </c>
       <c r="R2" t="n">
-        <v>7287871</v>
+        <v>7287851</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,12 +769,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,12 +784,7 @@
         <v>119219024</v>
       </c>
       <c r="B3" t="n">
-        <v>91824</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,12 +801,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -888,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119820315</v>
+        <v>119820316</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>687881</v>
+        <v>687827</v>
       </c>
       <c r="R4" t="n">
-        <v>7287907</v>
+        <v>7287900</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119820319</v>
+        <v>119218812</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,41 +995,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Akkavare, Pi lm</t>
+          <t>Storholmsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>687754</v>
+        <v>687770</v>
       </c>
       <c r="R5" t="n">
-        <v>7287850</v>
+        <v>7287904</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,17 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,49 +1069,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119820320</v>
+        <v>119820315</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1154,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>687754</v>
+        <v>687881</v>
       </c>
       <c r="R6" t="n">
-        <v>7287850</v>
+        <v>7287907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,15 +1187,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119820313</v>
+        <v>119218696</v>
       </c>
       <c r="B7" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,21 +1198,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,19 +1220,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Akkavare, Pi lm</t>
+          <t>Storholmsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>687718</v>
+        <v>687619</v>
       </c>
       <c r="R7" t="n">
-        <v>7287851</v>
+        <v>7287871</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,17 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,12 +1281,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1335,12 +1296,7 @@
         <v>119820317</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,15 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119820316</v>
+        <v>119820319</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1487,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>687827</v>
+        <v>687754</v>
       </c>
       <c r="R9" t="n">
-        <v>7287900</v>
+        <v>7287850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,15 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119820314</v>
+        <v>119218743</v>
       </c>
       <c r="B10" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1592,19 +1538,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Akkavare, Pi lm</t>
+          <t>Storholmsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688018</v>
+        <v>687699</v>
       </c>
       <c r="R10" t="n">
-        <v>7287704</v>
+        <v>7287903</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1628,17 +1579,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,27 +1599,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119820318</v>
+        <v>119221034</v>
       </c>
       <c r="B11" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1703,19 +1644,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Akkavare, Pi lm</t>
+          <t>Storholmsberget, Pi lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>687804</v>
+        <v>688153</v>
       </c>
       <c r="R11" t="n">
-        <v>7287873</v>
+        <v>7287832</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1739,17 +1685,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,15 +1705,662 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119820320</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Akkavare, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>687754</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7287850</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119218842</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storholmsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>687770</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7287904</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119220885</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storholmsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>688137</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7287859</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119220382</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storholmsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>688112</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7287885</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119218761</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storholmsberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>687724</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7287901</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>John-Olof Halvarsson, Ingunn Woldmo</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119820318</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Akkavare, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>687804</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7287873</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56413-2025 artfynd.xlsx
+++ b/artfynd/A 56413-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820316</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119218812</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820315</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119218696</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820317</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820319</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1608,6 +1653,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119218743</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119221034</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1820,6 +1875,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820320</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119218842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2052,6 +2117,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220885</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119220382</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2255,6 +2330,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119218761</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2361,8 +2441,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119820318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>